--- a/STA380GroupForm.xlsx
+++ b/STA380GroupForm.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasmi\Desktop\Study\2025-2026\Winter\sta380_repo\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C140A3-4321-491B-A505-69C46209DD43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -28,6 +35,9 @@
     <t>Group Name:</t>
   </si>
   <si>
+    <t>Team Chris</t>
+  </si>
+  <si>
     <t>Desired Topics:</t>
   </si>
   <si>
@@ -43,6 +53,15 @@
     <t>Topic Number 2</t>
   </si>
   <si>
+    <t>Robustness of models with different loss functions and estators under distribution shift</t>
+  </si>
+  <si>
+    <t>We consider the following data-generating process: X = theta + epsilon where theta is a fixed true value, and the noise term epsilon follows two possible distributions: 1. Standard Gaussian noise: epsilon ~ N(0, 1);  2. Abnormal noise after distribution shift, for example a mixture model: (1 - alpha)N(0, 1) + alphaN(0, sigma^2) where alpha represents the proportion (or strength) of unusual noise, and sigma controls the intensity of the outlier component. For the model, we will use a simple linear regression setting.</t>
+  </si>
+  <si>
+    <t>In this project, we will study how different estimators and loss functions perform when the training distribution is different from the testing distribution. The main goal is to use Monte Carlo simulations to show that when data noise changes from ideal Gaussian noise to heavy-tailed noise or noise with outliers, models based on the mean estimator and MSE loss become very unstable. In contrast, robust loss functions (such as Huber loss and MAE) and robust estimators (such as the median and trimmed mean) can maintain more stable performance. A Shiny web application will allow users to interactively adjust the strength of the distribution shift and observe in real time how estimation errors change under different distributions.</t>
+  </si>
+  <si>
     <t>Topic Number 3</t>
   </si>
   <si>
@@ -64,12 +83,48 @@
     <t>Student 1</t>
   </si>
   <si>
+    <t>Renfei Wu</t>
+  </si>
+  <si>
+    <t>wurenfei</t>
+  </si>
+  <si>
+    <t>chr1sren</t>
+  </si>
+  <si>
+    <t>https://github.com/chr1sren</t>
+  </si>
+  <si>
     <t>Student 2</t>
   </si>
   <si>
+    <t>Shiqi Tian</t>
+  </si>
+  <si>
+    <t>tianshi8</t>
+  </si>
+  <si>
+    <t>Dream-ABC</t>
+  </si>
+  <si>
+    <t>https://github.com/Dream-ABC</t>
+  </si>
+  <si>
     <t>Student 3</t>
   </si>
   <si>
+    <t>Chengxi Li</t>
+  </si>
+  <si>
+    <t>liche146</t>
+  </si>
+  <si>
+    <t>Togata1</t>
+  </si>
+  <si>
+    <t>https://github.com/Togata1</t>
+  </si>
+  <si>
     <t>Student 4</t>
   </si>
   <si>
@@ -86,59 +141,31 @@
   </si>
   <si>
     <t>To report an inactive member, please refer to the "Reporting Inactive Members" section under the project description.</t>
-  </si>
-  <si>
-    <t>Renfei Wu</t>
-  </si>
-  <si>
-    <t>wurenfei</t>
-  </si>
-  <si>
-    <t>chr1sren</t>
-  </si>
-  <si>
-    <t>https://github.com/chr1sren</t>
-  </si>
-  <si>
-    <t>In this project, we will study how different estimators and loss functions perform when the training distribution is different from the testing distribution. The main goal is to use Monte Carlo simulations to show that when data noise changes from ideal Gaussian noise to heavy-tailed noise or noise with outliers, models based on the mean estimator and MSE loss become very unstable. In contrast, robust loss functions (such as Huber loss and MAE) and robust estimators (such as the median and trimmed mean) can maintain more stable performance. A Shiny web application will allow users to interactively adjust the strength of the distribution shift and observe in real time how estimation errors change under different distributions.</t>
-  </si>
-  <si>
-    <t>We consider the following data-generating process: X = theta + epsilon where theta is a fixed true value, and the noise term epsilon follows two possible distributions: 1. Standard Gaussian noise: epsilon ~ N(0, 1);  2. Abnormal noise after distribution shift, for example a mixture model: (1 - alpha)N(0, 1) + alphaN(0, sigma^2) where alpha represents the proportion (or strength) of unusual noise, and sigma controls the intensity of the outlier component. For the model, we will use a simple linear regression setting.</t>
-  </si>
-  <si>
-    <t>Robustness of models with different loss functions and estators under distribution shift</t>
-  </si>
-  <si>
-    <t>Team Chris</t>
-  </si>
-  <si>
-    <t>Shiqi Tian</t>
-  </si>
-  <si>
-    <t>tianshi8</t>
-  </si>
-  <si>
-    <t>https://github.com/Dream-ABC</t>
-  </si>
-  <si>
-    <t>Dream-ABC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -147,6 +174,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -154,17 +182,169 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,8 +357,194 @@
         <bgColor rgb="FFC9DAF8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -186,29 +552,316 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -406,27 +1059,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="31.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="13.7809523809524" customWidth="1"/>
+    <col min="3" max="3" width="15.1047619047619" customWidth="1"/>
+    <col min="4" max="4" width="18.1047619047619" customWidth="1"/>
+    <col min="5" max="5" width="16.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="13.1047619047619" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -434,185 +1086,204 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" customHeight="1" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" customHeight="1" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:1">
       <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:1">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:1">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:2">
+      <c r="A10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:2">
+      <c r="A11" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:2">
+      <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:1">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:1">
+      <c r="A14" s="3"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:1">
+      <c r="A15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:1">
+      <c r="A16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" customHeight="1" spans="1:1">
       <c r="A17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:1">
       <c r="A18" s="3"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" customHeight="1" spans="1:6">
       <c r="A20" s="1"/>
       <c r="B20" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>23</v>
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="D21">
         <v>1009998237</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:6">
+      <c r="A22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
         <v>24</v>
-      </c>
-      <c r="F21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" t="s">
-        <v>31</v>
       </c>
       <c r="D22">
         <v>1009834654</v>
       </c>
       <c r="E22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:6">
+      <c r="A23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23">
+        <v>1008554734</v>
+      </c>
+      <c r="E23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:1">
+      <c r="A24" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:1">
+      <c r="A25" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>21</v>
+    </row>
+    <row r="27" customHeight="1" spans="1:1">
+      <c r="A27" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:1">
+      <c r="A28" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:1">
+      <c r="A29" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:1">
+      <c r="A30" s="6" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F23" r:id="rId1" display="https://github.com/Togata1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>